--- a/离线语言_协议/词表协议.xlsx
+++ b/离线语言_协议/词表协议.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
   <si>
     <t>Hello Bed</t>
   </si>
@@ -53,67 +53,184 @@
     <t>A5 FA 00 81 06 00 26 FB</t>
   </si>
   <si>
+    <t>A5 FA 00 81 07 00 27 FB</t>
+  </si>
+  <si>
+    <t>Tv preset</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 08 00 28 FB</t>
+  </si>
+  <si>
+    <t>Raise-head</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 09 00 29 FB</t>
+  </si>
+  <si>
+    <t>Lower-head</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0A 00 2A FB</t>
+  </si>
+  <si>
+    <t>Raise-foot</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0B 00 2B FB</t>
+  </si>
+  <si>
+    <t>Lower foot</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0C 00 2C FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0D 00 2D FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0E 00 2E FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0F 00 2F FB</t>
+  </si>
+  <si>
+    <t>MASSAGE OFF</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 10 00 30 FB</t>
+  </si>
+  <si>
+    <t>LIGHT OFF</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 11 00 31 FB</t>
+  </si>
+  <si>
+    <t>LIGHT ON</t>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送协议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOOD NIGHT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zero G/ZERO-GRAVITY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ANTI-SNORE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAISE LUMBAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOWER LUMBAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAISE TILT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOWER TILT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage UP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage Dwon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 21 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 02 00 22 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 21 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 82 01 00 22 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用唤醒词1唤醒，屏蔽唤醒词2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用唤醒词2唤醒，屏蔽唤醒词1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音芯片关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 20 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hello Ergo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 32 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 13 00 33 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 14 00 34 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 15 00 35 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 16 00 36 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 17 00 37 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 18 00 38 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Favorite preset</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 07 00 27 FB</t>
-  </si>
-  <si>
-    <t>Tv preset</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 08 00 28 FB</t>
-  </si>
-  <si>
-    <t>Raise-head</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 09 00 29 FB</t>
-  </si>
-  <si>
-    <t>Lower-head</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0A 00 2A FB</t>
-  </si>
-  <si>
-    <t>Raise-foot</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0B 00 2B FB</t>
-  </si>
-  <si>
-    <t>Lower foot</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0C 00 2C FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0D 00 2D FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0E 00 2E FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0F 00 2F FB</t>
-  </si>
-  <si>
-    <t>MASSAGE OFF</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 10 00 30 FB</t>
-  </si>
-  <si>
-    <t>LIGHT OFF</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 11 00 31 FB</t>
-  </si>
-  <si>
-    <t>LIGHT ON</t>
-  </si>
-  <si>
-    <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -121,15 +238,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>发送协议</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GOOD NIGHT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zero G/ZERO-GRAVITY</t>
+    <t>命令词（新版）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Favorite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL Flat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TV</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -137,107 +258,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RAISE LUMBAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOWER LUMBAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAISE TILT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOWER TILT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage On</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage UP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage Dwon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 21 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 02 00 22 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>接收</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 21 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 82 01 00 22 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用唤醒词1唤醒，屏蔽唤醒词2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用唤醒词2唤醒，屏蔽唤醒词1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语音芯片关闭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 20 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hello Ergo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 32 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 13 00 33 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 14 00 34 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 15 00 35 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 16 00 36 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 17 00 37 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 18 00 38 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令词（日语）</t>
+    <t>Lift Base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lower Base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 19 00 39 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 1A 00 3A FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整床抬升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整床降低</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -298,15 +339,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -467,35 +514,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -518,12 +541,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -804,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
@@ -816,19 +836,19 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>60</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
@@ -841,20 +861,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="22"/>
+        <v>50</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="D2" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1"/>
       <c r="G2" s="20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
       <c r="J2" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
@@ -866,17 +888,19 @@
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
       <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
       <c r="J3" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
@@ -888,17 +912,19 @@
       <c r="B4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="11" t="s">
+        <v>2</v>
+      </c>
       <c r="D4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -910,7 +936,9 @@
       <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="D5" s="12" t="s">
         <v>5</v>
       </c>
@@ -920,9 +948,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="23"/>
+        <v>31</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
@@ -934,7 +964,9 @@
       <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="24" t="s">
+        <v>62</v>
+      </c>
       <c r="D7" s="12" t="s">
         <v>8</v>
       </c>
@@ -944,11 +976,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>9</v>
-      </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="12" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -956,11 +990,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -968,11 +1004,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -980,11 +1018,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="12" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -992,11 +1032,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1004,11 +1046,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>19</v>
-      </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="12" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1016,11 +1060,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="24"/>
+        <v>37</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="D14" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1028,11 +1074,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="D15" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1040,11 +1088,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="24"/>
+        <v>39</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="D16" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1052,11 +1102,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>24</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="12" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1064,11 +1116,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1076,11 +1130,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="25"/>
+        <v>27</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="D19" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1088,11 +1144,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="18"/>
+        <v>30</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>30</v>
+      </c>
       <c r="D20" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,11 +1158,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="18"/>
+        <v>32</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>64</v>
+      </c>
       <c r="D21" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,11 +1172,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="18"/>
+        <v>33</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>33</v>
+      </c>
       <c r="D22" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1124,11 +1186,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="18"/>
+        <v>34</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="D23" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1136,11 +1200,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="18"/>
+        <v>35</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>35</v>
+      </c>
       <c r="D24" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1148,35 +1214,63 @@
         <v>24</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="18"/>
+        <v>36</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="D25" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+      <c r="A26" s="22"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="22"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
         <v>25</v>
       </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="8"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="20"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
